--- a/data/source/participantes-sorteo.xlsx
+++ b/data/source/participantes-sorteo.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FBD2BAA-4FC6-4040-BEF8-9F8C1E1F09EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{443E5A07-2EAE-4E02-8E08-9D9154C85191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="77">
   <si>
     <t>nombre_completo</t>
   </si>
@@ -256,10 +256,7 @@
     <t>numero</t>
   </si>
   <si>
-    <t>INCOGNITO</t>
-  </si>
-  <si>
-    <t>i</t>
+    <t>Dario Alberto Guevara</t>
   </si>
 </sst>
 </file>
@@ -1126,10 +1123,13 @@
         <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="C19" t="s">
         <v>76</v>
+      </c>
+      <c r="D19">
+        <v>3117205310</v>
       </c>
       <c r="G19">
         <v>18</v>
